--- a/data/trans_orig/IQ09_A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_A-Edad-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en años que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses)</t>
+          <t>Tiempo medio en años que llevan sufriendo esa dolencia, enfermedad o impedimento que les haya limitado de forma continuada (más de 10 días en los últimos 12 meses) (tasa de respuesta: 97,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,17 +716,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,66</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,01</t>
+          <t>0,12; 0,96</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 0,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,82</t>
+          <t>0,0; 0,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,98</t>
+          <t>0,15; 1,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,21</t>
+          <t>0,09; 1,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,22; 0,8</t>
+          <t>0,24; 0,81</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,87</t>
+          <t>0,0; 0,89</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,01</t>
+          <t>1,52; 4,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 3,11</t>
+          <t>0,82; 3,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,15</t>
+          <t>0,9; 3,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,02</t>
+          <t>0,8; 5,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,21</t>
+          <t>1,15; 4,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,86</t>
+          <t>0,81; 2,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,65</t>
+          <t>0,48; 2,76</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,18; 4,01</t>
+          <t>1,15; 4,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,8</t>
+          <t>1,71; 3,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,56</t>
+          <t>0,96; 2,52</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,65</t>
+          <t>0,91; 2,71</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,9</t>
+          <t>1,36; 3,81</t>
         </is>
       </c>
     </row>
@@ -996,27 +996,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,55; 7,14</t>
+          <t>0,54; 7,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,99</t>
+          <t>0,92; 5,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,79</t>
+          <t>0,0; 4,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,55</t>
+          <t>0,9; 5,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,74; 6,84</t>
+          <t>1,79; 6,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1026,32 +1026,32 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,69</t>
+          <t>1,05; 5,69</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 4,81</t>
+          <t>1,46; 5,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,92</t>
+          <t>1,91; 6,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 5,3</t>
+          <t>1,26; 5,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,1</t>
+          <t>0,93; 4,06</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,49</t>
+          <t>1,63; 4,35</t>
         </is>
       </c>
     </row>
@@ -1141,57 +1141,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 7,95</t>
+          <t>1,71; 7,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 8,13</t>
+          <t>0,7; 8,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,04</t>
+          <t>1,94; 8,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,24; 10,49</t>
+          <t>1,15; 9,81</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,14; 7,05</t>
+          <t>2,41; 7,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,57; 9,52</t>
+          <t>1,75; 10,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 10,53</t>
+          <t>4,51; 10,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 8,63</t>
+          <t>1,35; 8,78</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 6,56</t>
+          <t>2,63; 6,46</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,03; 7,76</t>
+          <t>1,92; 7,45</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,65; 8,51</t>
+          <t>3,77; 8,41</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 4,53</t>
+          <t>1,31; 4,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,17</t>
+          <t>1,35; 3,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,0; 3,39</t>
+          <t>0,9; 3,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,94; 4,64</t>
+          <t>1,91; 4,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 5,16</t>
+          <t>1,98; 4,93</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,67; 4,2</t>
+          <t>1,69; 4,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,75</t>
+          <t>1,35; 3,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 5,91</t>
+          <t>2,88; 5,83</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,17</t>
+          <t>1,98; 4,18</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 3,22</t>
+          <t>1,73; 3,24</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 2,94</t>
+          <t>1,37; 2,92</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,77; 4,91</t>
+          <t>2,72; 4,82</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_A-Edad-trans_orig.xlsx
@@ -721,12 +721,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,12; 0,96</t>
+          <t>0,13; 1,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,99</t>
+          <t>0,0; 0,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,83</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,0</t>
+          <t>0,16; 0,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -756,17 +756,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,09; 1,16</t>
+          <t>0,1; 1,16</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 0,81</t>
+          <t>0,21; 0,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,84</t>
+          <t>0,14; 0,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,14</t>
+          <t>1,53; 4,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,1</t>
+          <t>0,74; 3,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,08</t>
+          <t>0,86; 3,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 5,25</t>
+          <t>0,77; 4,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,16</t>
+          <t>1,21; 4,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,81; 2,78</t>
+          <t>0,76; 2,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,76</t>
+          <t>0,53; 2,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,1</t>
+          <t>1,17; 4,18</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,8</t>
+          <t>1,7; 3,74</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,96; 2,52</t>
+          <t>0,99; 2,54</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,71</t>
+          <t>0,87; 2,58</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,36; 3,81</t>
+          <t>1,43; 4,02</t>
         </is>
       </c>
     </row>
@@ -996,12 +996,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 7,14</t>
+          <t>0,55; 7,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,05</t>
+          <t>0,87; 5,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1011,47 +1011,47 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 5,74</t>
+          <t>0,9; 5,6</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 6,99</t>
+          <t>1,81; 7,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,8</t>
+          <t>0,0; 7,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,69</t>
+          <t>1,25; 6,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,33</t>
+          <t>1,29; 4,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,3</t>
+          <t>1,85; 6,26</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,26; 5,0</t>
+          <t>1,29; 5,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,06</t>
+          <t>1,02; 4,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,35</t>
+          <t>1,54; 4,4</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1141,12 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 7,86</t>
+          <t>1,79; 8,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,7; 8,26</t>
+          <t>0,72; 9,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1156,42 +1156,42 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 9,81</t>
+          <t>1,24; 10,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,22</t>
+          <t>2,37; 7,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,75; 10,8</t>
+          <t>1,69; 10,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,51; 10,26</t>
+          <t>4,59; 10,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 8,78</t>
+          <t>1,32; 9,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,63; 6,46</t>
+          <t>2,65; 6,32</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,92; 7,45</t>
+          <t>1,93; 7,63</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,41</t>
+          <t>3,78; 8,44</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,84</t>
+          <t>1,31; 4,51</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,23</t>
+          <t>1,29; 3,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,2</t>
+          <t>0,92; 3,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,54</t>
+          <t>2,1; 4,72</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,93</t>
+          <t>1,86; 4,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,69; 4,15</t>
+          <t>1,63; 4,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,35; 3,83</t>
+          <t>1,32; 3,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,88; 5,83</t>
+          <t>2,75; 5,9</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,18</t>
+          <t>1,97; 4,22</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,24</t>
+          <t>1,66; 3,21</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,92</t>
+          <t>1,32; 3,0</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 4,82</t>
+          <t>2,79; 4,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ09_A-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ09_A-Edad-trans_orig.xlsx
@@ -532,7 +532,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -540,7 +540,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -648,42 +648,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,45</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,61</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,67</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,48</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>0,24</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,62</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,45</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,61</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0</t>
+          <t>0,64</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,42</t>
+          <t>0,44</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 0,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,01</t>
+          <t>0,09; 0,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,97</t>
+          <t>0,18; 1,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 1,66</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,14; 1,01</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,98</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 1,0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,82</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0,16; 0,98</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,18; 1,0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,16</t>
+          <t>0,1; 1,21</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,21; 0,79</t>
+          <t>0,22; 0,8</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,14; 0,86</t>
+          <t>0,14; 0,84</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,89</t>
+          <t>0,0; 0,88</t>
         </is>
       </c>
     </row>
@@ -788,62 +788,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2,67</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,51</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,42</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2,4</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>2,95</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>1,85</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>1,89</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2,71</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>2,78</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1,67</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1,59</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>2,52</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,67</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,51</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,42</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2,41</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2,78</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1,67</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>1,59</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>2,45</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,06</t>
+          <t>1,35; 4,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,22</t>
+          <t>0,75; 2,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,08</t>
+          <t>0,41; 2,65</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,72</t>
+          <t>1,14; 4,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,21; 4,16</t>
+          <t>1,3; 4,01</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,83</t>
+          <t>0,68; 3,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,93</t>
+          <t>0,97; 3,15</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,17; 4,18</t>
+          <t>1,02; 5,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,74</t>
+          <t>1,86; 3,8</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,54</t>
+          <t>1,03; 2,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,58</t>
+          <t>0,83; 2,65</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,02</t>
+          <t>1,47; 4,04</t>
         </is>
       </c>
     </row>
@@ -928,42 +928,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,14</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3,34</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2,87</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,75</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2,99</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2,68</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>1,59</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,64</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,14</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,34</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2,87</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,86</t>
+          <t>2,7</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>2,73</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1,74; 6,84</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,8</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1,25; 5,69</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1,19; 4,73</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
           <t>0,55; 7,14</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0,87; 5,28</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,07</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,9; 5,6</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,81; 7,28</t>
-        </is>
-      </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,76</t>
+          <t>0,87; 4,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 6,21</t>
+          <t>0,0; 3,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 4,8</t>
+          <t>0,99; 5,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 6,26</t>
+          <t>1,86; 5,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,29; 5,19</t>
+          <t>1,3; 5,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,3</t>
+          <t>0,98; 4,1</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,4</t>
+          <t>1,56; 4,55</t>
         </is>
       </c>
     </row>
@@ -1068,42 +1068,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,59</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4,56</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5,04</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7,05</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,57</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,47</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2,88</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,33</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,59</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,56</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,04</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,99</t>
+          <t>6,02</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,74</t>
+          <t>6,73</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1136,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1,24; 10,49</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2,14; 7,05</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1,57; 9,52</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4,58; 10,77</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 10,64</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>1,79; 8,93</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0,72; 9,36</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1,94; 8,93</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1,24; 10,07</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,37; 7,39</t>
+          <t>1,72; 7,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 10,88</t>
+          <t>0,74; 8,13</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,59; 10,42</t>
+          <t>1,75; 10,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 9,02</t>
+          <t>1,33; 8,63</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 6,32</t>
+          <t>2,52; 6,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 7,63</t>
+          <t>2,03; 7,76</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,78; 8,44</t>
+          <t>4,38; 9,7</t>
         </is>
       </c>
     </row>
@@ -1208,42 +1208,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>3,12</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,67</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2,29</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>4,18</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>2,56</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2,02</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,66</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>3,1</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>3,12</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>2,67</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4,1</t>
+          <t>3,32</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,66</t>
+          <t>3,83</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 4,51</t>
+          <t>1,98; 5,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,15</t>
+          <t>1,67; 4,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,22</t>
+          <t>1,36; 3,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,72</t>
+          <t>2,85; 6,14</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,79</t>
+          <t>1,3; 4,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,11</t>
+          <t>1,31; 3,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,8</t>
+          <t>1,0; 3,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 5,9</t>
+          <t>1,88; 5,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,22</t>
+          <t>1,91; 4,17</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,21</t>
+          <t>1,63; 3,22</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,0</t>
+          <t>1,29; 2,94</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,79; 4,93</t>
+          <t>2,84; 5,34</t>
         </is>
       </c>
     </row>
